--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY156"/>
+  <dimension ref="A1:AZ156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -808,6 +813,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775033</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -944,6 +954,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775034</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1198,6 +1218,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775096</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1305,6 +1330,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1412,6 +1442,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774571</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1519,6 +1554,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774574</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1626,6 +1666,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774620</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1733,6 +1778,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775028</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1840,6 +1890,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775036</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775046</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775062</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2161,6 +2226,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775076</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2268,6 +2338,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775089</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2375,6 +2450,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775080</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2502,6 +2582,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774576</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2629,6 +2714,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774589</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2756,6 +2846,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774592</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2883,6 +2978,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774593</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3010,6 +3110,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774596</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3137,6 +3242,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774604</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3264,6 +3374,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774626</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3391,6 +3506,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774636</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3518,6 +3638,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3645,6 +3770,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774650</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3772,6 +3902,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774668</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3884,6 +4019,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774640</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4011,6 +4151,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774622</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4118,6 +4263,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774603</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4245,6 +4395,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774606</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4372,6 +4527,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774615</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4499,6 +4659,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774625</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4626,6 +4791,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774638</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4753,6 +4923,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774641</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4880,6 +5055,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774666</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5007,6 +5187,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774674</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5114,6 +5299,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774605</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5221,6 +5411,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774672</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5328,6 +5523,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775079</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5435,6 +5635,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774627</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5542,6 +5747,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5649,6 +5859,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775107</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5756,6 +5971,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774618</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5863,6 +6083,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774649</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5970,6 +6195,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775091</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6077,6 +6307,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775101</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6184,6 +6419,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774599</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6291,6 +6531,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775083</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6398,6 +6643,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774569</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6514,6 +6764,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774572</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6621,6 +6876,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774598</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6728,6 +6988,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774671</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6849,6 +7114,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774578</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6965,6 +7235,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774607</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7081,6 +7356,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774610</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7202,6 +7482,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774628</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7323,6 +7608,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774629</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7439,6 +7729,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774630</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7555,6 +7850,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774631</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7671,6 +7971,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774632</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7787,6 +8092,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774633</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7908,6 +8218,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774634</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8024,6 +8339,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774635</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8140,6 +8460,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774639</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8261,6 +8586,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774643</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8377,6 +8707,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774647</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8493,6 +8828,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774665</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8609,6 +8949,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774669</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8725,6 +9070,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774673</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8841,6 +9191,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774675</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8957,6 +9312,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775039</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9073,6 +9433,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775040</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9189,6 +9554,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775048</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9305,6 +9675,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775054</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9421,6 +9796,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775055</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9537,6 +9917,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775056</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9653,6 +10038,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775065</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9769,6 +10159,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775067</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9885,6 +10280,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775069</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10001,6 +10401,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775070</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10117,6 +10522,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775084</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10233,6 +10643,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775099</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10349,6 +10764,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775104</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10465,6 +10885,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775105</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10581,6 +11006,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775111</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10697,6 +11127,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775113</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10813,6 +11248,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775114</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10929,6 +11369,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775115</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11045,6 +11490,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775116</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11161,6 +11611,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775117</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11277,6 +11732,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775118</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11393,6 +11853,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775119</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11509,6 +11974,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775120</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11625,6 +12095,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774579</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11741,6 +12216,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774580</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11857,6 +12337,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774583</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11973,6 +12458,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774584</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12089,6 +12579,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774585</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12205,6 +12700,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774590</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12321,6 +12821,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774611</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12437,6 +12942,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774623</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12553,6 +13063,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774624</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12669,6 +13184,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774662</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12785,6 +13305,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774663</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12901,6 +13426,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775050</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13017,6 +13547,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775051</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13133,6 +13668,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775057</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13249,6 +13789,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775058</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13370,6 +13915,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775064</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13486,6 +14036,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775066</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13602,6 +14157,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775071</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13713,6 +14273,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775100</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13820,6 +14385,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774566</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13927,6 +14497,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774568</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14034,6 +14609,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774570</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14141,6 +14721,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774573</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14248,6 +14833,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774582</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14355,6 +14945,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774587</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14462,6 +15057,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774597</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14569,6 +15169,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774601</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14676,6 +15281,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774608</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14783,6 +15393,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774612</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14890,6 +15505,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774617</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14997,6 +15617,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774644</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15104,6 +15729,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774648</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15211,6 +15841,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774670</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15318,6 +15953,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774676</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15425,6 +16065,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775023</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15532,6 +16177,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775024</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15639,6 +16289,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775027</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15746,6 +16401,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775029</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15853,6 +16513,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775030</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15960,6 +16625,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775031</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16067,6 +16737,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775032</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16174,6 +16849,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775035</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16281,6 +16961,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775042</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16388,6 +17073,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775044</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16495,6 +17185,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775045</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16602,6 +17297,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775047</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16709,6 +17409,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775049</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16816,6 +17521,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775052</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16923,6 +17633,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775059</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -17030,6 +17745,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775060</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -17137,6 +17857,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775068</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17244,6 +17969,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775072</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17351,6 +18081,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775073</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17458,6 +18193,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775074</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17565,6 +18305,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775075</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17672,6 +18417,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775085</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17779,6 +18529,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775088</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17886,6 +18641,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775098</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17993,6 +18753,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775102</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -18100,6 +18865,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775108</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18207,6 +18977,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775110</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18314,8 +19089,170 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134774677</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ156"/>
+  <dimension ref="A1:AZ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,32 +2458,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134774576</v>
+        <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>75468</v>
+        <v>92512</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>5420</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>699463</v>
+        <v>699910</v>
       </c>
       <c r="R17" t="n">
-        <v>6687421</v>
+        <v>6686788</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2523,22 +2523,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2549,48 +2539,28 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774576</t>
+          <t>https://artportalen.se/Sighting/136472418</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134774589</v>
+        <v>134774576</v>
       </c>
       <c r="B18" t="n">
         <v>75468</v>
@@ -2625,10 +2595,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>699524</v>
+        <v>699463</v>
       </c>
       <c r="R18" t="n">
-        <v>6687447</v>
+        <v>6687421</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2660,7 +2630,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2670,7 +2640,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2716,13 +2686,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774589</t>
+          <t>https://artportalen.se/Sighting/134774576</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134774592</v>
+        <v>134774589</v>
       </c>
       <c r="B19" t="n">
         <v>75468</v>
@@ -2757,10 +2727,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>699531</v>
+        <v>699524</v>
       </c>
       <c r="R19" t="n">
-        <v>6687408</v>
+        <v>6687447</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2792,7 +2762,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2802,7 +2772,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,13 +2818,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774592</t>
+          <t>https://artportalen.se/Sighting/134774589</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134774593</v>
+        <v>134774592</v>
       </c>
       <c r="B20" t="n">
         <v>75468</v>
@@ -2889,10 +2859,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>699539</v>
+        <v>699531</v>
       </c>
       <c r="R20" t="n">
-        <v>6687392</v>
+        <v>6687408</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2924,7 +2894,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2934,7 +2904,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2980,13 +2950,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774593</t>
+          <t>https://artportalen.se/Sighting/134774592</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134774596</v>
+        <v>134774593</v>
       </c>
       <c r="B21" t="n">
         <v>75468</v>
@@ -3021,10 +2991,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>699534</v>
+        <v>699539</v>
       </c>
       <c r="R21" t="n">
-        <v>6687386</v>
+        <v>6687392</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3056,7 +3026,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3066,7 +3036,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3112,13 +3082,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774596</t>
+          <t>https://artportalen.se/Sighting/134774593</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134774604</v>
+        <v>134774596</v>
       </c>
       <c r="B22" t="n">
         <v>75468</v>
@@ -3153,10 +3123,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>699577</v>
+        <v>699534</v>
       </c>
       <c r="R22" t="n">
-        <v>6687355</v>
+        <v>6687386</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3188,7 +3158,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3198,7 +3168,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3244,13 +3214,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774604</t>
+          <t>https://artportalen.se/Sighting/134774596</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134774626</v>
+        <v>134774604</v>
       </c>
       <c r="B23" t="n">
         <v>75468</v>
@@ -3285,10 +3255,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>699632</v>
+        <v>699577</v>
       </c>
       <c r="R23" t="n">
-        <v>6687111</v>
+        <v>6687355</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3320,7 +3290,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3330,7 +3300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3376,13 +3346,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774626</t>
+          <t>https://artportalen.se/Sighting/134774604</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134774636</v>
+        <v>134774626</v>
       </c>
       <c r="B24" t="n">
         <v>75468</v>
@@ -3417,10 +3387,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>699745</v>
+        <v>699632</v>
       </c>
       <c r="R24" t="n">
-        <v>6687015</v>
+        <v>6687111</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3452,7 +3422,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3462,7 +3432,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3508,13 +3478,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774636</t>
+          <t>https://artportalen.se/Sighting/134774626</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134774646</v>
+        <v>134774636</v>
       </c>
       <c r="B25" t="n">
         <v>75468</v>
@@ -3549,10 +3519,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>699649</v>
+        <v>699745</v>
       </c>
       <c r="R25" t="n">
-        <v>6687299</v>
+        <v>6687015</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3584,7 +3554,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3594,7 +3564,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3640,13 +3610,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774646</t>
+          <t>https://artportalen.se/Sighting/134774636</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134774650</v>
+        <v>134774646</v>
       </c>
       <c r="B26" t="n">
         <v>75468</v>
@@ -3681,10 +3651,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>699616</v>
+        <v>699649</v>
       </c>
       <c r="R26" t="n">
-        <v>6687443</v>
+        <v>6687299</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3716,7 +3686,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3726,7 +3696,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3772,13 +3742,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774650</t>
+          <t>https://artportalen.se/Sighting/134774646</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134774668</v>
+        <v>134774650</v>
       </c>
       <c r="B27" t="n">
         <v>75468</v>
@@ -3813,10 +3783,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>699863</v>
+        <v>699616</v>
       </c>
       <c r="R27" t="n">
-        <v>6686833</v>
+        <v>6687443</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3843,22 +3813,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3904,56 +3874,51 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774668</t>
+          <t>https://artportalen.se/Sighting/134774650</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134774640</v>
+        <v>134774668</v>
       </c>
       <c r="B28" t="n">
-        <v>57972</v>
+        <v>75468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>699770</v>
+        <v>699863</v>
       </c>
       <c r="R28" t="n">
-        <v>6687083</v>
+        <v>6686833</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3980,22 +3945,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4006,6 +3971,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4021,16 +4006,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774640</t>
+          <t>https://artportalen.se/Sighting/134774668</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134774622</v>
+        <v>134774640</v>
       </c>
       <c r="B29" t="n">
-        <v>5181</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4038,34 +4023,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>699609</v>
+        <v>699770</v>
       </c>
       <c r="R29" t="n">
-        <v>6687117</v>
+        <v>6687083</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4097,7 +4087,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4107,7 +4097,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4118,26 +4108,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4153,16 +4123,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774622</t>
+          <t>https://artportalen.se/Sighting/134774640</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134774603</v>
+        <v>134774622</v>
       </c>
       <c r="B30" t="n">
-        <v>4782</v>
+        <v>5181</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4170,21 +4140,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4194,10 +4164,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>699561</v>
+        <v>699609</v>
       </c>
       <c r="R30" t="n">
-        <v>6687353</v>
+        <v>6687117</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4229,7 +4199,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4239,7 +4209,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4250,6 +4220,26 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4265,13 +4255,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774603</t>
+          <t>https://artportalen.se/Sighting/134774622</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134774606</v>
+        <v>134774603</v>
       </c>
       <c r="B31" t="n">
         <v>4782</v>
@@ -4306,10 +4296,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>699584</v>
+        <v>699561</v>
       </c>
       <c r="R31" t="n">
-        <v>6687318</v>
+        <v>6687353</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4341,7 +4331,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4351,7 +4341,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4362,26 +4352,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4397,13 +4367,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774606</t>
+          <t>https://artportalen.se/Sighting/134774603</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134774615</v>
+        <v>134774606</v>
       </c>
       <c r="B32" t="n">
         <v>4782</v>
@@ -4438,10 +4408,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>699610</v>
+        <v>699584</v>
       </c>
       <c r="R32" t="n">
-        <v>6687133</v>
+        <v>6687318</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4473,7 +4443,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4483,7 +4453,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4529,13 +4499,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774615</t>
+          <t>https://artportalen.se/Sighting/134774606</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134774625</v>
+        <v>134774615</v>
       </c>
       <c r="B33" t="n">
         <v>4782</v>
@@ -4570,10 +4540,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>699626</v>
+        <v>699610</v>
       </c>
       <c r="R33" t="n">
-        <v>6687110</v>
+        <v>6687133</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4605,7 +4575,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4615,7 +4585,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4661,13 +4631,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774625</t>
+          <t>https://artportalen.se/Sighting/134774615</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134774638</v>
+        <v>134774625</v>
       </c>
       <c r="B34" t="n">
         <v>4782</v>
@@ -4702,10 +4672,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>699751</v>
+        <v>699626</v>
       </c>
       <c r="R34" t="n">
-        <v>6687043</v>
+        <v>6687110</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4737,7 +4707,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4747,7 +4717,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4793,13 +4763,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774638</t>
+          <t>https://artportalen.se/Sighting/134774625</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134774641</v>
+        <v>134774638</v>
       </c>
       <c r="B35" t="n">
         <v>4782</v>
@@ -4834,10 +4804,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>699780</v>
+        <v>699751</v>
       </c>
       <c r="R35" t="n">
-        <v>6687088</v>
+        <v>6687043</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4869,7 +4839,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4879,7 +4849,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4925,13 +4895,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774641</t>
+          <t>https://artportalen.se/Sighting/134774638</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134774666</v>
+        <v>134774641</v>
       </c>
       <c r="B36" t="n">
         <v>4782</v>
@@ -4966,10 +4936,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>699859</v>
+        <v>699780</v>
       </c>
       <c r="R36" t="n">
-        <v>6686835</v>
+        <v>6687088</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4996,22 +4966,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5057,13 +5027,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774666</t>
+          <t>https://artportalen.se/Sighting/134774641</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134774674</v>
+        <v>134774666</v>
       </c>
       <c r="B37" t="n">
         <v>4782</v>
@@ -5098,10 +5068,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>699649</v>
+        <v>699859</v>
       </c>
       <c r="R37" t="n">
-        <v>6687303</v>
+        <v>6686835</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5133,7 +5103,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5143,7 +5113,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5189,16 +5159,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774674</t>
+          <t>https://artportalen.se/Sighting/134774666</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134774605</v>
+        <v>134774674</v>
       </c>
       <c r="B38" t="n">
-        <v>5201</v>
+        <v>4782</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5206,21 +5176,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5230,10 +5200,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>699586</v>
+        <v>699649</v>
       </c>
       <c r="R38" t="n">
-        <v>6687317</v>
+        <v>6687303</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -5260,22 +5230,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5286,6 +5256,26 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5301,13 +5291,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774605</t>
+          <t>https://artportalen.se/Sighting/134774674</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134774672</v>
+        <v>134774605</v>
       </c>
       <c r="B39" t="n">
         <v>5201</v>
@@ -5342,10 +5332,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>699777</v>
+        <v>699586</v>
       </c>
       <c r="R39" t="n">
-        <v>6686890</v>
+        <v>6687317</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5372,22 +5362,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5413,13 +5403,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774672</t>
+          <t>https://artportalen.se/Sighting/134774605</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134775079</v>
+        <v>134774672</v>
       </c>
       <c r="B40" t="n">
         <v>5201</v>
@@ -5454,10 +5444,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>700261</v>
+        <v>699777</v>
       </c>
       <c r="R40" t="n">
-        <v>6686998</v>
+        <v>6686890</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5489,7 +5479,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5499,7 +5489,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5525,16 +5515,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775079</t>
+          <t>https://artportalen.se/Sighting/134774672</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134774627</v>
+        <v>134775079</v>
       </c>
       <c r="B41" t="n">
-        <v>8449</v>
+        <v>5201</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5542,21 +5532,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5566,13 +5556,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>699649</v>
+        <v>700261</v>
       </c>
       <c r="R41" t="n">
-        <v>6687110</v>
+        <v>6686998</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5596,22 +5586,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5637,13 +5627,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774627</t>
+          <t>https://artportalen.se/Sighting/134775079</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134775025</v>
+        <v>134774627</v>
       </c>
       <c r="B42" t="n">
         <v>8449</v>
@@ -5678,13 +5668,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>700152</v>
+        <v>699649</v>
       </c>
       <c r="R42" t="n">
-        <v>6687290</v>
+        <v>6687110</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5708,22 +5698,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5749,13 +5739,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775025</t>
+          <t>https://artportalen.se/Sighting/134774627</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134775107</v>
+        <v>134775025</v>
       </c>
       <c r="B43" t="n">
         <v>8449</v>
@@ -5790,10 +5780,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>700173</v>
+        <v>700152</v>
       </c>
       <c r="R43" t="n">
-        <v>6686889</v>
+        <v>6687290</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5825,7 +5815,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5835,7 +5825,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5861,38 +5851,38 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775107</t>
+          <t>https://artportalen.se/Sighting/134775025</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134774618</v>
+        <v>134775107</v>
       </c>
       <c r="B44" t="n">
-        <v>111471</v>
+        <v>8449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219711</v>
+        <v>106554</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5902,10 +5892,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>699608</v>
+        <v>700173</v>
       </c>
       <c r="R44" t="n">
-        <v>6687129</v>
+        <v>6686889</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5932,22 +5922,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5973,13 +5963,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774618</t>
+          <t>https://artportalen.se/Sighting/134775107</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134774649</v>
+        <v>134774618</v>
       </c>
       <c r="B45" t="n">
         <v>111471</v>
@@ -6014,10 +6004,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>699611</v>
+        <v>699608</v>
       </c>
       <c r="R45" t="n">
-        <v>6687375</v>
+        <v>6687129</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6049,7 +6039,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6059,7 +6049,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6085,13 +6075,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774649</t>
+          <t>https://artportalen.se/Sighting/134774618</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134775091</v>
+        <v>134774649</v>
       </c>
       <c r="B46" t="n">
         <v>111471</v>
@@ -6126,10 +6116,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>700199</v>
+        <v>699611</v>
       </c>
       <c r="R46" t="n">
-        <v>6686934</v>
+        <v>6687375</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6156,22 +6146,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6197,13 +6187,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775091</t>
+          <t>https://artportalen.se/Sighting/134774649</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134775101</v>
+        <v>134775091</v>
       </c>
       <c r="B47" t="n">
         <v>111471</v>
@@ -6238,10 +6228,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>700118</v>
+        <v>700199</v>
       </c>
       <c r="R47" t="n">
-        <v>6686872</v>
+        <v>6686934</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6273,7 +6263,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6283,7 +6273,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6309,38 +6299,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775101</t>
+          <t>https://artportalen.se/Sighting/134775091</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134774599</v>
+        <v>134775101</v>
       </c>
       <c r="B48" t="n">
-        <v>99219</v>
+        <v>111471</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6350,10 +6340,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>699533</v>
+        <v>700118</v>
       </c>
       <c r="R48" t="n">
-        <v>6687377</v>
+        <v>6686872</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6380,22 +6370,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6421,38 +6411,38 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774599</t>
+          <t>https://artportalen.se/Sighting/134775101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134775083</v>
+        <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>99219</v>
+        <v>111635</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219847</v>
+        <v>219711</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6462,13 +6452,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>700211</v>
+        <v>700271</v>
       </c>
       <c r="R49" t="n">
-        <v>6686971</v>
+        <v>6686946</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6492,22 +6482,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6522,27 +6502,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775083</t>
+          <t>https://artportalen.se/Sighting/136472416</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134774569</v>
+        <v>134774599</v>
       </c>
       <c r="B50" t="n">
-        <v>99218</v>
+        <v>99219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6550,21 +6530,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6574,13 +6554,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>699414</v>
+        <v>699533</v>
       </c>
       <c r="R50" t="n">
-        <v>6687478</v>
+        <v>6687377</v>
       </c>
       <c r="S50" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6609,7 +6589,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6619,7 +6599,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6645,16 +6625,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774569</t>
+          <t>https://artportalen.se/Sighting/134774599</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134774572</v>
+        <v>134775083</v>
       </c>
       <c r="B51" t="n">
-        <v>99218</v>
+        <v>99219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6662,46 +6642,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219862</v>
+        <v>219847</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>699433</v>
+        <v>700211</v>
       </c>
       <c r="R51" t="n">
-        <v>6687475</v>
+        <v>6686971</v>
       </c>
       <c r="S51" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6725,22 +6696,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,16 +6737,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774572</t>
+          <t>https://artportalen.se/Sighting/134775083</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134774598</v>
+        <v>134774569</v>
       </c>
       <c r="B52" t="n">
-        <v>99230</v>
+        <v>99218</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6783,16 +6754,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219874</v>
+        <v>219862</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6807,13 +6778,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>699533</v>
+        <v>699414</v>
       </c>
       <c r="R52" t="n">
-        <v>6687377</v>
+        <v>6687478</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6842,7 +6813,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6852,7 +6823,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6878,16 +6849,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774598</t>
+          <t>https://artportalen.se/Sighting/134774569</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134774671</v>
+        <v>134774572</v>
       </c>
       <c r="B53" t="n">
-        <v>99230</v>
+        <v>99218</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6895,16 +6866,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219874</v>
+        <v>219862</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6912,20 +6883,29 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>699817</v>
+        <v>699433</v>
       </c>
       <c r="R53" t="n">
-        <v>6686871</v>
+        <v>6687475</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6949,22 +6929,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6990,68 +6970,54 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774671</t>
+          <t>https://artportalen.se/Sighting/134774572</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134774578</v>
+        <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99195</v>
+        <v>99364</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>219862</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>699457</v>
+        <v>699591</v>
       </c>
       <c r="R54" t="n">
-        <v>6687414</v>
+        <v>6687355</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7075,22 +7041,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7105,71 +7061,62 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774578</t>
+          <t>https://artportalen.se/Sighting/136472421</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134774607</v>
+        <v>134774598</v>
       </c>
       <c r="B55" t="n">
-        <v>99195</v>
+        <v>99230</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>699566</v>
+        <v>699533</v>
       </c>
       <c r="R55" t="n">
-        <v>6687324</v>
+        <v>6687377</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -7201,7 +7148,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7211,7 +7158,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7237,60 +7184,51 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774607</t>
+          <t>https://artportalen.se/Sighting/134774598</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134774610</v>
+        <v>134774671</v>
       </c>
       <c r="B56" t="n">
-        <v>99195</v>
+        <v>99230</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>699559</v>
+        <v>699817</v>
       </c>
       <c r="R56" t="n">
-        <v>6687232</v>
+        <v>6686871</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -7317,22 +7255,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7358,13 +7296,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774610</t>
+          <t>https://artportalen.se/Sighting/134774671</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134774628</v>
+        <v>134774578</v>
       </c>
       <c r="B57" t="n">
         <v>99195</v>
@@ -7394,7 +7332,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7413,10 +7351,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>699631</v>
+        <v>699457</v>
       </c>
       <c r="R57" t="n">
-        <v>6687071</v>
+        <v>6687414</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -7448,7 +7386,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7458,7 +7396,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7484,13 +7422,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774628</t>
+          <t>https://artportalen.se/Sighting/134774578</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134774629</v>
+        <v>134774607</v>
       </c>
       <c r="B58" t="n">
         <v>99195</v>
@@ -7520,7 +7458,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -7528,21 +7466,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>699629</v>
+        <v>699566</v>
       </c>
       <c r="R58" t="n">
-        <v>6687067</v>
+        <v>6687324</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7574,7 +7507,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7584,7 +7517,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7610,13 +7543,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774629</t>
+          <t>https://artportalen.se/Sighting/134774607</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134774630</v>
+        <v>134774610</v>
       </c>
       <c r="B59" t="n">
         <v>99195</v>
@@ -7646,7 +7579,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -7660,10 +7593,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>699627</v>
+        <v>699559</v>
       </c>
       <c r="R59" t="n">
-        <v>6687065</v>
+        <v>6687232</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7695,7 +7628,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7705,7 +7638,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7731,13 +7664,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774630</t>
+          <t>https://artportalen.se/Sighting/134774610</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134774631</v>
+        <v>134774628</v>
       </c>
       <c r="B60" t="n">
         <v>99195</v>
@@ -7767,7 +7700,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -7775,16 +7708,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>699606</v>
+        <v>699631</v>
       </c>
       <c r="R60" t="n">
-        <v>6687005</v>
+        <v>6687071</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7816,7 +7754,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7826,7 +7764,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7852,13 +7790,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774631</t>
+          <t>https://artportalen.se/Sighting/134774628</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134774632</v>
+        <v>134774629</v>
       </c>
       <c r="B61" t="n">
         <v>99195</v>
@@ -7888,7 +7826,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -7896,16 +7834,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>699620</v>
+        <v>699629</v>
       </c>
       <c r="R61" t="n">
-        <v>6686972</v>
+        <v>6687067</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7937,7 +7880,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7947,7 +7890,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7973,13 +7916,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774632</t>
+          <t>https://artportalen.se/Sighting/134774629</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134774633</v>
+        <v>134774630</v>
       </c>
       <c r="B62" t="n">
         <v>99195</v>
@@ -8009,7 +7952,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -8023,10 +7966,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>699592</v>
+        <v>699627</v>
       </c>
       <c r="R62" t="n">
-        <v>6686931</v>
+        <v>6687065</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8058,7 +8001,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8068,7 +8011,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8094,13 +8037,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774633</t>
+          <t>https://artportalen.se/Sighting/134774630</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134774634</v>
+        <v>134774631</v>
       </c>
       <c r="B63" t="n">
         <v>99195</v>
@@ -8130,7 +8073,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -8138,21 +8081,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>699658</v>
+        <v>699606</v>
       </c>
       <c r="R63" t="n">
-        <v>6686931</v>
+        <v>6687005</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8184,7 +8122,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8194,7 +8132,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8220,13 +8158,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774634</t>
+          <t>https://artportalen.se/Sighting/134774631</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134774635</v>
+        <v>134774632</v>
       </c>
       <c r="B64" t="n">
         <v>99195</v>
@@ -8256,7 +8194,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8270,10 +8208,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>699735</v>
+        <v>699620</v>
       </c>
       <c r="R64" t="n">
-        <v>6687006</v>
+        <v>6686972</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -8305,7 +8243,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8315,7 +8253,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8341,13 +8279,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774635</t>
+          <t>https://artportalen.se/Sighting/134774632</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134774639</v>
+        <v>134774633</v>
       </c>
       <c r="B65" t="n">
         <v>99195</v>
@@ -8377,7 +8315,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8391,10 +8329,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>699749</v>
+        <v>699592</v>
       </c>
       <c r="R65" t="n">
-        <v>6687070</v>
+        <v>6686931</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -8426,7 +8364,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8436,7 +8374,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8462,13 +8400,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774639</t>
+          <t>https://artportalen.se/Sighting/134774633</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134774643</v>
+        <v>134774634</v>
       </c>
       <c r="B66" t="n">
         <v>99195</v>
@@ -8498,7 +8436,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8508,7 +8446,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8517,13 +8455,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>699721</v>
+        <v>699658</v>
       </c>
       <c r="R66" t="n">
-        <v>6687188</v>
+        <v>6686931</v>
       </c>
       <c r="S66" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8552,7 +8490,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8562,7 +8500,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8588,13 +8526,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774643</t>
+          <t>https://artportalen.se/Sighting/134774634</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134774647</v>
+        <v>134774635</v>
       </c>
       <c r="B67" t="n">
         <v>99195</v>
@@ -8624,7 +8562,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -8638,10 +8576,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>699648</v>
+        <v>699735</v>
       </c>
       <c r="R67" t="n">
-        <v>6687306</v>
+        <v>6687006</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8673,7 +8611,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8683,7 +8621,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8709,13 +8647,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774647</t>
+          <t>https://artportalen.se/Sighting/134774635</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134774665</v>
+        <v>134774639</v>
       </c>
       <c r="B68" t="n">
         <v>99195</v>
@@ -8745,7 +8683,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -8759,10 +8697,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>699919</v>
+        <v>699749</v>
       </c>
       <c r="R68" t="n">
-        <v>6686794</v>
+        <v>6687070</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8789,22 +8727,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8830,13 +8768,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774665</t>
+          <t>https://artportalen.se/Sighting/134774639</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134774669</v>
+        <v>134774643</v>
       </c>
       <c r="B69" t="n">
         <v>99195</v>
@@ -8866,7 +8804,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -8874,19 +8812,24 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>699853</v>
+        <v>699721</v>
       </c>
       <c r="R69" t="n">
-        <v>6686846</v>
+        <v>6687188</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8910,22 +8853,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8951,13 +8894,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774669</t>
+          <t>https://artportalen.se/Sighting/134774643</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134774673</v>
+        <v>134774647</v>
       </c>
       <c r="B70" t="n">
         <v>99195</v>
@@ -8987,7 +8930,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9001,10 +8944,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>699765</v>
+        <v>699648</v>
       </c>
       <c r="R70" t="n">
-        <v>6686883</v>
+        <v>6687306</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -9031,22 +8974,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9072,13 +9015,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774673</t>
+          <t>https://artportalen.se/Sighting/134774647</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134774675</v>
+        <v>134774665</v>
       </c>
       <c r="B71" t="n">
         <v>99195</v>
@@ -9108,7 +9051,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9122,10 +9065,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>699646</v>
+        <v>699919</v>
       </c>
       <c r="R71" t="n">
-        <v>6687309</v>
+        <v>6686794</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -9157,7 +9100,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9167,7 +9110,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9193,13 +9136,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774675</t>
+          <t>https://artportalen.se/Sighting/134774665</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134775039</v>
+        <v>134774669</v>
       </c>
       <c r="B72" t="n">
         <v>99195</v>
@@ -9229,7 +9172,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9243,10 +9186,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>700115</v>
+        <v>699853</v>
       </c>
       <c r="R72" t="n">
-        <v>6687198</v>
+        <v>6686846</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -9278,7 +9221,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9288,7 +9231,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9314,13 +9257,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775039</t>
+          <t>https://artportalen.se/Sighting/134774669</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134775040</v>
+        <v>134774673</v>
       </c>
       <c r="B73" t="n">
         <v>99195</v>
@@ -9350,7 +9293,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9364,10 +9307,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>700111</v>
+        <v>699765</v>
       </c>
       <c r="R73" t="n">
-        <v>6687193</v>
+        <v>6686883</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -9399,7 +9342,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9409,7 +9352,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9435,13 +9378,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775040</t>
+          <t>https://artportalen.se/Sighting/134774673</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134775048</v>
+        <v>134774675</v>
       </c>
       <c r="B74" t="n">
         <v>99195</v>
@@ -9471,7 +9414,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9485,10 +9428,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>700113</v>
+        <v>699646</v>
       </c>
       <c r="R74" t="n">
-        <v>6687102</v>
+        <v>6687309</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9520,7 +9463,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9530,7 +9473,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9556,13 +9499,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775048</t>
+          <t>https://artportalen.se/Sighting/134774675</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134775054</v>
+        <v>134775039</v>
       </c>
       <c r="B75" t="n">
         <v>99195</v>
@@ -9592,7 +9535,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -9606,13 +9549,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>700081</v>
+        <v>700115</v>
       </c>
       <c r="R75" t="n">
-        <v>6687100</v>
+        <v>6687198</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9641,7 +9584,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9651,7 +9594,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9677,13 +9620,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775054</t>
+          <t>https://artportalen.se/Sighting/134775039</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134775055</v>
+        <v>134775040</v>
       </c>
       <c r="B76" t="n">
         <v>99195</v>
@@ -9713,7 +9656,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9727,10 +9670,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>700084</v>
+        <v>700111</v>
       </c>
       <c r="R76" t="n">
-        <v>6687091</v>
+        <v>6687193</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9762,7 +9705,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9772,7 +9715,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9798,13 +9741,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775055</t>
+          <t>https://artportalen.se/Sighting/134775040</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134775056</v>
+        <v>134775048</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -9834,7 +9777,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9848,10 +9791,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>700093</v>
+        <v>700113</v>
       </c>
       <c r="R77" t="n">
-        <v>6687085</v>
+        <v>6687102</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9883,7 +9826,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9893,7 +9836,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9919,13 +9862,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775056</t>
+          <t>https://artportalen.se/Sighting/134775048</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134775065</v>
+        <v>134775054</v>
       </c>
       <c r="B78" t="n">
         <v>99195</v>
@@ -9969,13 +9912,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>700139</v>
+        <v>700081</v>
       </c>
       <c r="R78" t="n">
-        <v>6687048</v>
+        <v>6687100</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10004,7 +9947,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10014,7 +9957,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10040,13 +9983,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775065</t>
+          <t>https://artportalen.se/Sighting/134775054</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134775067</v>
+        <v>134775055</v>
       </c>
       <c r="B79" t="n">
         <v>99195</v>
@@ -10076,7 +10019,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -10090,10 +10033,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>700140</v>
+        <v>700084</v>
       </c>
       <c r="R79" t="n">
-        <v>6687045</v>
+        <v>6687091</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -10125,7 +10068,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10135,7 +10078,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10161,13 +10104,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775067</t>
+          <t>https://artportalen.se/Sighting/134775055</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134775069</v>
+        <v>134775056</v>
       </c>
       <c r="B80" t="n">
         <v>99195</v>
@@ -10197,7 +10140,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -10211,10 +10154,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>700150</v>
+        <v>700093</v>
       </c>
       <c r="R80" t="n">
-        <v>6687044</v>
+        <v>6687085</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -10246,7 +10189,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10256,7 +10199,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10282,13 +10225,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775069</t>
+          <t>https://artportalen.se/Sighting/134775056</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134775070</v>
+        <v>134775065</v>
       </c>
       <c r="B81" t="n">
         <v>99195</v>
@@ -10318,7 +10261,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -10332,13 +10275,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>700156</v>
+        <v>700139</v>
       </c>
       <c r="R81" t="n">
-        <v>6687042</v>
+        <v>6687048</v>
       </c>
       <c r="S81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10367,7 +10310,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10377,7 +10320,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10403,13 +10346,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775070</t>
+          <t>https://artportalen.se/Sighting/134775065</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134775084</v>
+        <v>134775067</v>
       </c>
       <c r="B82" t="n">
         <v>99195</v>
@@ -10439,7 +10382,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10453,10 +10396,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>700184</v>
+        <v>700140</v>
       </c>
       <c r="R82" t="n">
-        <v>6686976</v>
+        <v>6687045</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10488,7 +10431,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10498,7 +10441,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10524,13 +10467,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775084</t>
+          <t>https://artportalen.se/Sighting/134775067</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134775099</v>
+        <v>134775069</v>
       </c>
       <c r="B83" t="n">
         <v>99195</v>
@@ -10560,7 +10503,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10574,10 +10517,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>700117</v>
+        <v>700150</v>
       </c>
       <c r="R83" t="n">
-        <v>6686874</v>
+        <v>6687044</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10609,7 +10552,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10619,7 +10562,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10645,13 +10588,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775099</t>
+          <t>https://artportalen.se/Sighting/134775069</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134775104</v>
+        <v>134775070</v>
       </c>
       <c r="B84" t="n">
         <v>99195</v>
@@ -10681,7 +10624,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -10695,10 +10638,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>700150</v>
+        <v>700156</v>
       </c>
       <c r="R84" t="n">
-        <v>6686839</v>
+        <v>6687042</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10730,7 +10673,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10740,7 +10683,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10766,13 +10709,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775104</t>
+          <t>https://artportalen.se/Sighting/134775070</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134775105</v>
+        <v>134775084</v>
       </c>
       <c r="B85" t="n">
         <v>99195</v>
@@ -10802,7 +10745,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -10816,10 +10759,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>700159</v>
+        <v>700184</v>
       </c>
       <c r="R85" t="n">
-        <v>6686836</v>
+        <v>6686976</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10851,7 +10794,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10861,7 +10804,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10887,13 +10830,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775105</t>
+          <t>https://artportalen.se/Sighting/134775084</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134775111</v>
+        <v>134775099</v>
       </c>
       <c r="B86" t="n">
         <v>99195</v>
@@ -10923,7 +10866,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -10937,10 +10880,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>700345</v>
+        <v>700117</v>
       </c>
       <c r="R86" t="n">
-        <v>6686891</v>
+        <v>6686874</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10972,7 +10915,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10982,7 +10925,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11008,13 +10951,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775111</t>
+          <t>https://artportalen.se/Sighting/134775099</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134775113</v>
+        <v>134775104</v>
       </c>
       <c r="B87" t="n">
         <v>99195</v>
@@ -11044,7 +10987,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11058,10 +11001,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>700373</v>
+        <v>700150</v>
       </c>
       <c r="R87" t="n">
-        <v>6686857</v>
+        <v>6686839</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -11093,7 +11036,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11103,7 +11046,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11129,13 +11072,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775113</t>
+          <t>https://artportalen.se/Sighting/134775104</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134775114</v>
+        <v>134775105</v>
       </c>
       <c r="B88" t="n">
         <v>99195</v>
@@ -11165,7 +11108,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11179,10 +11122,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>700372</v>
+        <v>700159</v>
       </c>
       <c r="R88" t="n">
-        <v>6686854</v>
+        <v>6686836</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -11214,7 +11157,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11224,7 +11167,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11250,13 +11193,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775114</t>
+          <t>https://artportalen.se/Sighting/134775105</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134775115</v>
+        <v>134775111</v>
       </c>
       <c r="B89" t="n">
         <v>99195</v>
@@ -11286,7 +11229,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11300,10 +11243,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>700373</v>
+        <v>700345</v>
       </c>
       <c r="R89" t="n">
-        <v>6686850</v>
+        <v>6686891</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11335,7 +11278,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11345,7 +11288,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11371,13 +11314,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775115</t>
+          <t>https://artportalen.se/Sighting/134775111</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134775116</v>
+        <v>134775113</v>
       </c>
       <c r="B90" t="n">
         <v>99195</v>
@@ -11407,7 +11350,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -11421,10 +11364,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>700383</v>
+        <v>700373</v>
       </c>
       <c r="R90" t="n">
-        <v>6686811</v>
+        <v>6686857</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -11456,7 +11399,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11466,7 +11409,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11492,13 +11435,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775116</t>
+          <t>https://artportalen.se/Sighting/134775113</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134775117</v>
+        <v>134775114</v>
       </c>
       <c r="B91" t="n">
         <v>99195</v>
@@ -11528,7 +11471,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -11542,10 +11485,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>700379</v>
+        <v>700372</v>
       </c>
       <c r="R91" t="n">
-        <v>6686808</v>
+        <v>6686854</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -11577,7 +11520,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11587,7 +11530,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11613,13 +11556,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775117</t>
+          <t>https://artportalen.se/Sighting/134775114</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134775118</v>
+        <v>134775115</v>
       </c>
       <c r="B92" t="n">
         <v>99195</v>
@@ -11649,7 +11592,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -11663,10 +11606,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>700356</v>
+        <v>700373</v>
       </c>
       <c r="R92" t="n">
-        <v>6686782</v>
+        <v>6686850</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11698,7 +11641,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11708,7 +11651,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11734,13 +11677,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775118</t>
+          <t>https://artportalen.se/Sighting/134775115</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134775119</v>
+        <v>134775116</v>
       </c>
       <c r="B93" t="n">
         <v>99195</v>
@@ -11770,7 +11713,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -11784,10 +11727,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>700358</v>
+        <v>700383</v>
       </c>
       <c r="R93" t="n">
-        <v>6686778</v>
+        <v>6686811</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11819,7 +11762,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11829,7 +11772,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11855,13 +11798,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775119</t>
+          <t>https://artportalen.se/Sighting/134775116</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134775120</v>
+        <v>134775117</v>
       </c>
       <c r="B94" t="n">
         <v>99195</v>
@@ -11891,7 +11834,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -11905,10 +11848,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>700358</v>
+        <v>700379</v>
       </c>
       <c r="R94" t="n">
-        <v>6686774</v>
+        <v>6686808</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11940,7 +11883,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11950,7 +11893,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11976,43 +11919,43 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775120</t>
+          <t>https://artportalen.se/Sighting/134775117</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134774579</v>
+        <v>134775118</v>
       </c>
       <c r="B95" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -12026,10 +11969,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>699463</v>
+        <v>700356</v>
       </c>
       <c r="R95" t="n">
-        <v>6687413</v>
+        <v>6686782</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -12056,22 +11999,22 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -12097,43 +12040,43 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774579</t>
+          <t>https://artportalen.se/Sighting/134775118</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>134774580</v>
+        <v>134775119</v>
       </c>
       <c r="B96" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -12147,10 +12090,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>699466</v>
+        <v>700358</v>
       </c>
       <c r="R96" t="n">
-        <v>6687407</v>
+        <v>6686778</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -12177,22 +12120,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12218,43 +12161,43 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774580</t>
+          <t>https://artportalen.se/Sighting/134775119</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134774583</v>
+        <v>134775120</v>
       </c>
       <c r="B97" t="n">
-        <v>106324</v>
+        <v>99195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -12268,10 +12211,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>699483</v>
+        <v>700358</v>
       </c>
       <c r="R97" t="n">
-        <v>6687410</v>
+        <v>6686774</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -12298,22 +12241,22 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12339,63 +12282,54 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774583</t>
+          <t>https://artportalen.se/Sighting/134775120</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134774584</v>
+        <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>106324</v>
+        <v>99341</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>699505</v>
+        <v>700076</v>
       </c>
       <c r="R98" t="n">
-        <v>6687430</v>
+        <v>6686857</v>
       </c>
       <c r="S98" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12419,22 +12353,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12449,74 +12373,65 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774584</t>
+          <t>https://artportalen.se/Sighting/136472417</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134774585</v>
+        <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>106324</v>
+        <v>99341</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>699504</v>
+        <v>699742</v>
       </c>
       <c r="R99" t="n">
-        <v>6687432</v>
+        <v>6687078</v>
       </c>
       <c r="S99" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12540,22 +12455,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12570,24 +12475,24 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774585</t>
+          <t>https://artportalen.se/Sighting/136472419</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>134774590</v>
+        <v>134774579</v>
       </c>
       <c r="B100" t="n">
         <v>106324</v>
@@ -12617,7 +12522,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -12631,10 +12536,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>699526</v>
+        <v>699463</v>
       </c>
       <c r="R100" t="n">
-        <v>6687437</v>
+        <v>6687413</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -12666,7 +12571,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12676,7 +12581,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12702,13 +12607,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774590</t>
+          <t>https://artportalen.se/Sighting/134774579</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>134774611</v>
+        <v>134774580</v>
       </c>
       <c r="B101" t="n">
         <v>106324</v>
@@ -12738,7 +12643,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -12752,10 +12657,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>699557</v>
+        <v>699466</v>
       </c>
       <c r="R101" t="n">
-        <v>6687214</v>
+        <v>6687407</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -12787,7 +12692,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12797,7 +12702,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12823,13 +12728,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774611</t>
+          <t>https://artportalen.se/Sighting/134774580</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134774623</v>
+        <v>134774583</v>
       </c>
       <c r="B102" t="n">
         <v>106324</v>
@@ -12859,7 +12764,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -12873,10 +12778,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>699605</v>
+        <v>699483</v>
       </c>
       <c r="R102" t="n">
-        <v>6687115</v>
+        <v>6687410</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -12908,7 +12813,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12918,7 +12823,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12944,13 +12849,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774623</t>
+          <t>https://artportalen.se/Sighting/134774583</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134774624</v>
+        <v>134774584</v>
       </c>
       <c r="B103" t="n">
         <v>106324</v>
@@ -12980,7 +12885,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12994,10 +12899,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>699606</v>
+        <v>699505</v>
       </c>
       <c r="R103" t="n">
-        <v>6687113</v>
+        <v>6687430</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -13029,7 +12934,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -13039,7 +12944,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -13065,13 +12970,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774624</t>
+          <t>https://artportalen.se/Sighting/134774584</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134774662</v>
+        <v>134774585</v>
       </c>
       <c r="B104" t="n">
         <v>106324</v>
@@ -13101,7 +13006,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -13115,10 +13020,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>699874</v>
+        <v>699504</v>
       </c>
       <c r="R104" t="n">
-        <v>6686760</v>
+        <v>6687432</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -13145,22 +13050,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -13186,13 +13091,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774662</t>
+          <t>https://artportalen.se/Sighting/134774585</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>134774663</v>
+        <v>134774590</v>
       </c>
       <c r="B105" t="n">
         <v>106324</v>
@@ -13222,7 +13127,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -13236,10 +13141,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>699872</v>
+        <v>699526</v>
       </c>
       <c r="R105" t="n">
-        <v>6686767</v>
+        <v>6687437</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -13266,22 +13171,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13307,13 +13212,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774663</t>
+          <t>https://artportalen.se/Sighting/134774590</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>134775050</v>
+        <v>134774611</v>
       </c>
       <c r="B106" t="n">
         <v>106324</v>
@@ -13343,7 +13248,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -13357,10 +13262,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>700109</v>
+        <v>699557</v>
       </c>
       <c r="R106" t="n">
-        <v>6687093</v>
+        <v>6687214</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -13387,22 +13292,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13428,13 +13333,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775050</t>
+          <t>https://artportalen.se/Sighting/134774611</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134775051</v>
+        <v>134774623</v>
       </c>
       <c r="B107" t="n">
         <v>106324</v>
@@ -13464,7 +13369,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -13478,10 +13383,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>700108</v>
+        <v>699605</v>
       </c>
       <c r="R107" t="n">
-        <v>6687092</v>
+        <v>6687115</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>
@@ -13508,22 +13413,22 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13549,13 +13454,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775051</t>
+          <t>https://artportalen.se/Sighting/134774623</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134775057</v>
+        <v>134774624</v>
       </c>
       <c r="B108" t="n">
         <v>106324</v>
@@ -13585,7 +13490,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -13599,10 +13504,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>700111</v>
+        <v>699606</v>
       </c>
       <c r="R108" t="n">
-        <v>6687073</v>
+        <v>6687113</v>
       </c>
       <c r="S108" t="n">
         <v>5</v>
@@ -13629,22 +13534,22 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13670,13 +13575,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775057</t>
+          <t>https://artportalen.se/Sighting/134774624</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>134775058</v>
+        <v>134774662</v>
       </c>
       <c r="B109" t="n">
         <v>106324</v>
@@ -13706,7 +13611,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>80</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
@@ -13720,10 +13625,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>700115</v>
+        <v>699874</v>
       </c>
       <c r="R109" t="n">
-        <v>6687073</v>
+        <v>6686760</v>
       </c>
       <c r="S109" t="n">
         <v>5</v>
@@ -13755,7 +13660,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13765,7 +13670,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13791,13 +13696,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775058</t>
+          <t>https://artportalen.se/Sighting/134774662</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>134775064</v>
+        <v>134774663</v>
       </c>
       <c r="B110" t="n">
         <v>106324</v>
@@ -13827,7 +13732,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -13835,21 +13740,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>700127</v>
+        <v>699872</v>
       </c>
       <c r="R110" t="n">
-        <v>6687068</v>
+        <v>6686767</v>
       </c>
       <c r="S110" t="n">
         <v>5</v>
@@ -13881,7 +13781,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13891,7 +13791,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13917,13 +13817,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775064</t>
+          <t>https://artportalen.se/Sighting/134774663</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134775066</v>
+        <v>134775050</v>
       </c>
       <c r="B111" t="n">
         <v>106324</v>
@@ -13953,7 +13853,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -13967,10 +13867,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>700136</v>
+        <v>700109</v>
       </c>
       <c r="R111" t="n">
-        <v>6687047</v>
+        <v>6687093</v>
       </c>
       <c r="S111" t="n">
         <v>5</v>
@@ -14002,7 +13902,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -14012,7 +13912,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -14038,13 +13938,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775066</t>
+          <t>https://artportalen.se/Sighting/134775050</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134775071</v>
+        <v>134775051</v>
       </c>
       <c r="B112" t="n">
         <v>106324</v>
@@ -14074,7 +13974,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -14088,10 +13988,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>700154</v>
+        <v>700108</v>
       </c>
       <c r="R112" t="n">
-        <v>6687033</v>
+        <v>6687092</v>
       </c>
       <c r="S112" t="n">
         <v>5</v>
@@ -14123,7 +14023,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -14133,7 +14033,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -14159,13 +14059,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775071</t>
+          <t>https://artportalen.se/Sighting/134775051</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134775100</v>
+        <v>134775057</v>
       </c>
       <c r="B113" t="n">
         <v>106324</v>
@@ -14195,7 +14095,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -14204,10 +14109,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>700117</v>
+        <v>700111</v>
       </c>
       <c r="R113" t="n">
-        <v>6686874</v>
+        <v>6687073</v>
       </c>
       <c r="S113" t="n">
         <v>5</v>
@@ -14239,7 +14144,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14249,7 +14154,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14275,16 +14180,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775100</t>
+          <t>https://artportalen.se/Sighting/134775057</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134774566</v>
+        <v>134775058</v>
       </c>
       <c r="B114" t="n">
-        <v>101403</v>
+        <v>106324</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14292,37 +14197,46 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>699424</v>
+        <v>700115</v>
       </c>
       <c r="R114" t="n">
-        <v>6687512</v>
+        <v>6687073</v>
       </c>
       <c r="S114" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14346,22 +14260,22 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14387,16 +14301,16 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774566</t>
+          <t>https://artportalen.se/Sighting/134775058</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134774568</v>
+        <v>134775064</v>
       </c>
       <c r="B115" t="n">
-        <v>101403</v>
+        <v>106324</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14404,34 +14318,48 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>699406</v>
+        <v>700127</v>
       </c>
       <c r="R115" t="n">
-        <v>6687485</v>
+        <v>6687068</v>
       </c>
       <c r="S115" t="n">
         <v>5</v>
@@ -14458,22 +14386,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14499,16 +14427,16 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774568</t>
+          <t>https://artportalen.se/Sighting/134775064</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>134774570</v>
+        <v>134775066</v>
       </c>
       <c r="B116" t="n">
-        <v>101403</v>
+        <v>106324</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14516,34 +14444,43 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>699426</v>
+        <v>700136</v>
       </c>
       <c r="R116" t="n">
-        <v>6687469</v>
+        <v>6687047</v>
       </c>
       <c r="S116" t="n">
         <v>5</v>
@@ -14570,22 +14507,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14611,16 +14548,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774570</t>
+          <t>https://artportalen.se/Sighting/134775066</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>134774573</v>
+        <v>134775071</v>
       </c>
       <c r="B117" t="n">
-        <v>101403</v>
+        <v>106324</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14628,34 +14565,43 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>699449</v>
+        <v>700154</v>
       </c>
       <c r="R117" t="n">
-        <v>6687454</v>
+        <v>6687033</v>
       </c>
       <c r="S117" t="n">
         <v>5</v>
@@ -14682,22 +14628,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14723,16 +14669,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774573</t>
+          <t>https://artportalen.se/Sighting/134775071</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>134774582</v>
+        <v>134775100</v>
       </c>
       <c r="B118" t="n">
-        <v>101403</v>
+        <v>106324</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14740,34 +14686,38 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>699484</v>
+        <v>700117</v>
       </c>
       <c r="R118" t="n">
-        <v>6687413</v>
+        <v>6686874</v>
       </c>
       <c r="S118" t="n">
         <v>5</v>
@@ -14794,22 +14744,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14835,16 +14785,16 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774582</t>
+          <t>https://artportalen.se/Sighting/134775100</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>134774587</v>
+        <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>101403</v>
+        <v>98209</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14852,21 +14802,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>222498</v>
+        <v>221941</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14876,13 +14826,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>699510</v>
+        <v>700070</v>
       </c>
       <c r="R119" t="n">
-        <v>6687437</v>
+        <v>6687145</v>
       </c>
       <c r="S119" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14906,22 +14856,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>12:30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14936,24 +14876,24 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Karin Wiklund</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774587</t>
+          <t>https://artportalen.se/Sighting/136472413</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>134774597</v>
+        <v>134774566</v>
       </c>
       <c r="B120" t="n">
         <v>101403</v>
@@ -14988,13 +14928,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>699532</v>
+        <v>699424</v>
       </c>
       <c r="R120" t="n">
-        <v>6687381</v>
+        <v>6687512</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -15023,7 +14963,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15033,7 +14973,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15059,13 +14999,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774597</t>
+          <t>https://artportalen.se/Sighting/134774566</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>134774601</v>
+        <v>134774568</v>
       </c>
       <c r="B121" t="n">
         <v>101403</v>
@@ -15100,10 +15040,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>699537</v>
+        <v>699406</v>
       </c>
       <c r="R121" t="n">
-        <v>6687375</v>
+        <v>6687485</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -15135,7 +15075,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15145,7 +15085,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15171,13 +15111,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774601</t>
+          <t>https://artportalen.se/Sighting/134774568</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>134774608</v>
+        <v>134774570</v>
       </c>
       <c r="B122" t="n">
         <v>101403</v>
@@ -15212,10 +15152,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>699533</v>
+        <v>699426</v>
       </c>
       <c r="R122" t="n">
-        <v>6687279</v>
+        <v>6687469</v>
       </c>
       <c r="S122" t="n">
         <v>5</v>
@@ -15247,7 +15187,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15257,7 +15197,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15283,13 +15223,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774608</t>
+          <t>https://artportalen.se/Sighting/134774570</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>134774612</v>
+        <v>134774573</v>
       </c>
       <c r="B123" t="n">
         <v>101403</v>
@@ -15324,10 +15264,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>699597</v>
+        <v>699449</v>
       </c>
       <c r="R123" t="n">
-        <v>6687178</v>
+        <v>6687454</v>
       </c>
       <c r="S123" t="n">
         <v>5</v>
@@ -15359,7 +15299,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -15369,7 +15309,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15395,13 +15335,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774612</t>
+          <t>https://artportalen.se/Sighting/134774573</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>134774617</v>
+        <v>134774582</v>
       </c>
       <c r="B124" t="n">
         <v>101403</v>
@@ -15436,10 +15376,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>699608</v>
+        <v>699484</v>
       </c>
       <c r="R124" t="n">
-        <v>6687129</v>
+        <v>6687413</v>
       </c>
       <c r="S124" t="n">
         <v>5</v>
@@ -15471,7 +15411,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -15481,7 +15421,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15507,13 +15447,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774617</t>
+          <t>https://artportalen.se/Sighting/134774582</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>134774644</v>
+        <v>134774587</v>
       </c>
       <c r="B125" t="n">
         <v>101403</v>
@@ -15548,10 +15488,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>699725</v>
+        <v>699510</v>
       </c>
       <c r="R125" t="n">
-        <v>6687191</v>
+        <v>6687437</v>
       </c>
       <c r="S125" t="n">
         <v>5</v>
@@ -15583,7 +15523,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15593,7 +15533,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15619,13 +15559,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774644</t>
+          <t>https://artportalen.se/Sighting/134774587</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>134774648</v>
+        <v>134774597</v>
       </c>
       <c r="B126" t="n">
         <v>101403</v>
@@ -15660,10 +15600,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>699625</v>
+        <v>699532</v>
       </c>
       <c r="R126" t="n">
-        <v>6687352</v>
+        <v>6687381</v>
       </c>
       <c r="S126" t="n">
         <v>5</v>
@@ -15695,7 +15635,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15705,7 +15645,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15731,13 +15671,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774648</t>
+          <t>https://artportalen.se/Sighting/134774597</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>134774670</v>
+        <v>134774601</v>
       </c>
       <c r="B127" t="n">
         <v>101403</v>
@@ -15772,10 +15712,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>699837</v>
+        <v>699537</v>
       </c>
       <c r="R127" t="n">
-        <v>6686855</v>
+        <v>6687375</v>
       </c>
       <c r="S127" t="n">
         <v>5</v>
@@ -15802,22 +15742,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15843,13 +15783,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774670</t>
+          <t>https://artportalen.se/Sighting/134774601</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134774676</v>
+        <v>134774608</v>
       </c>
       <c r="B128" t="n">
         <v>101403</v>
@@ -15884,10 +15824,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>699644</v>
+        <v>699533</v>
       </c>
       <c r="R128" t="n">
-        <v>6687321</v>
+        <v>6687279</v>
       </c>
       <c r="S128" t="n">
         <v>5</v>
@@ -15914,22 +15854,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15955,13 +15895,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134774676</t>
+          <t>https://artportalen.se/Sighting/134774608</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>134775023</v>
+        <v>134774612</v>
       </c>
       <c r="B129" t="n">
         <v>101403</v>
@@ -15996,10 +15936,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>700178</v>
+        <v>699597</v>
       </c>
       <c r="R129" t="n">
-        <v>6687313</v>
+        <v>6687178</v>
       </c>
       <c r="S129" t="n">
         <v>5</v>
@@ -16026,22 +15966,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -16067,13 +16007,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775023</t>
+          <t>https://artportalen.se/Sighting/134774612</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134775024</v>
+        <v>134774617</v>
       </c>
       <c r="B130" t="n">
         <v>101403</v>
@@ -16108,10 +16048,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>700157</v>
+        <v>699608</v>
       </c>
       <c r="R130" t="n">
-        <v>6687291</v>
+        <v>6687129</v>
       </c>
       <c r="S130" t="n">
         <v>5</v>
@@ -16138,22 +16078,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -16179,13 +16119,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775024</t>
+          <t>https://artportalen.se/Sighting/134774617</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134775027</v>
+        <v>134774644</v>
       </c>
       <c r="B131" t="n">
         <v>101403</v>
@@ -16220,10 +16160,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>700140</v>
+        <v>699725</v>
       </c>
       <c r="R131" t="n">
-        <v>6687288</v>
+        <v>6687191</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -16250,22 +16190,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16291,13 +16231,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775027</t>
+          <t>https://artportalen.se/Sighting/134774644</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134775029</v>
+        <v>134774648</v>
       </c>
       <c r="B132" t="n">
         <v>101403</v>
@@ -16332,10 +16272,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>700109</v>
+        <v>699625</v>
       </c>
       <c r="R132" t="n">
-        <v>6687254</v>
+        <v>6687352</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -16362,22 +16302,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16403,13 +16343,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775029</t>
+          <t>https://artportalen.se/Sighting/134774648</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134775030</v>
+        <v>134774670</v>
       </c>
       <c r="B133" t="n">
         <v>101403</v>
@@ -16444,10 +16384,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>700104</v>
+        <v>699837</v>
       </c>
       <c r="R133" t="n">
-        <v>6687298</v>
+        <v>6686855</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -16479,7 +16419,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16489,7 +16429,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16515,13 +16455,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775030</t>
+          <t>https://artportalen.se/Sighting/134774670</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134775031</v>
+        <v>134774676</v>
       </c>
       <c r="B134" t="n">
         <v>101403</v>
@@ -16556,10 +16496,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>700087</v>
+        <v>699644</v>
       </c>
       <c r="R134" t="n">
-        <v>6687320</v>
+        <v>6687321</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -16591,7 +16531,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16601,7 +16541,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>09:27</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16627,13 +16567,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775031</t>
+          <t>https://artportalen.se/Sighting/134774676</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134775032</v>
+        <v>134775023</v>
       </c>
       <c r="B135" t="n">
         <v>101403</v>
@@ -16668,10 +16608,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>700079</v>
+        <v>700178</v>
       </c>
       <c r="R135" t="n">
-        <v>6687292</v>
+        <v>6687313</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -16703,7 +16643,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16713,7 +16653,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>09:28</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16739,13 +16679,13 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775032</t>
+          <t>https://artportalen.se/Sighting/134775023</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>134775035</v>
+        <v>134775024</v>
       </c>
       <c r="B136" t="n">
         <v>101403</v>
@@ -16780,10 +16720,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>700063</v>
+        <v>700157</v>
       </c>
       <c r="R136" t="n">
-        <v>6687261</v>
+        <v>6687291</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -16815,7 +16755,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -16825,7 +16765,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16851,13 +16791,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775035</t>
+          <t>https://artportalen.se/Sighting/134775024</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>134775042</v>
+        <v>134775027</v>
       </c>
       <c r="B137" t="n">
         <v>101403</v>
@@ -16892,10 +16832,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>700125</v>
+        <v>700140</v>
       </c>
       <c r="R137" t="n">
-        <v>6687203</v>
+        <v>6687288</v>
       </c>
       <c r="S137" t="n">
         <v>5</v>
@@ -16927,7 +16867,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -16937,7 +16877,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16963,13 +16903,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775042</t>
+          <t>https://artportalen.se/Sighting/134775027</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134775044</v>
+        <v>134775029</v>
       </c>
       <c r="B138" t="n">
         <v>101403</v>
@@ -17004,10 +16944,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>700142</v>
+        <v>700109</v>
       </c>
       <c r="R138" t="n">
-        <v>6687183</v>
+        <v>6687254</v>
       </c>
       <c r="S138" t="n">
         <v>5</v>
@@ -17039,7 +16979,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -17049,7 +16989,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -17075,13 +17015,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775044</t>
+          <t>https://artportalen.se/Sighting/134775029</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>134775045</v>
+        <v>134775030</v>
       </c>
       <c r="B139" t="n">
         <v>101403</v>
@@ -17116,10 +17056,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>700129</v>
+        <v>700104</v>
       </c>
       <c r="R139" t="n">
-        <v>6687164</v>
+        <v>6687298</v>
       </c>
       <c r="S139" t="n">
         <v>5</v>
@@ -17151,7 +17091,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -17161,7 +17101,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -17187,13 +17127,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775045</t>
+          <t>https://artportalen.se/Sighting/134775030</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>134775047</v>
+        <v>134775031</v>
       </c>
       <c r="B140" t="n">
         <v>101403</v>
@@ -17228,10 +17168,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>700104</v>
+        <v>700087</v>
       </c>
       <c r="R140" t="n">
-        <v>6687135</v>
+        <v>6687320</v>
       </c>
       <c r="S140" t="n">
         <v>5</v>
@@ -17263,7 +17203,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -17273,7 +17213,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -17299,13 +17239,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775047</t>
+          <t>https://artportalen.se/Sighting/134775031</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134775049</v>
+        <v>134775032</v>
       </c>
       <c r="B141" t="n">
         <v>101403</v>
@@ -17340,10 +17280,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>700159</v>
+        <v>700079</v>
       </c>
       <c r="R141" t="n">
-        <v>6687105</v>
+        <v>6687292</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -17375,7 +17315,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -17385,7 +17325,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17411,13 +17351,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775049</t>
+          <t>https://artportalen.se/Sighting/134775032</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134775052</v>
+        <v>134775035</v>
       </c>
       <c r="B142" t="n">
         <v>101403</v>
@@ -17452,10 +17392,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>700094</v>
+        <v>700063</v>
       </c>
       <c r="R142" t="n">
-        <v>6687107</v>
+        <v>6687261</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -17487,7 +17427,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -17497,7 +17437,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -17523,13 +17463,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775052</t>
+          <t>https://artportalen.se/Sighting/134775035</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>134775059</v>
+        <v>134775042</v>
       </c>
       <c r="B143" t="n">
         <v>101403</v>
@@ -17564,10 +17504,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>700117</v>
+        <v>700125</v>
       </c>
       <c r="R143" t="n">
-        <v>6687077</v>
+        <v>6687203</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -17599,7 +17539,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -17609,7 +17549,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -17635,13 +17575,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775059</t>
+          <t>https://artportalen.se/Sighting/134775042</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>134775060</v>
+        <v>134775044</v>
       </c>
       <c r="B144" t="n">
         <v>101403</v>
@@ -17676,10 +17616,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>700141</v>
+        <v>700142</v>
       </c>
       <c r="R144" t="n">
-        <v>6687078</v>
+        <v>6687183</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -17711,7 +17651,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -17721,7 +17661,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -17747,13 +17687,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775060</t>
+          <t>https://artportalen.se/Sighting/134775044</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>134775068</v>
+        <v>134775045</v>
       </c>
       <c r="B145" t="n">
         <v>101403</v>
@@ -17788,10 +17728,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>700149</v>
+        <v>700129</v>
       </c>
       <c r="R145" t="n">
-        <v>6687048</v>
+        <v>6687164</v>
       </c>
       <c r="S145" t="n">
         <v>5</v>
@@ -17823,7 +17763,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -17833,7 +17773,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -17859,13 +17799,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775068</t>
+          <t>https://artportalen.se/Sighting/134775045</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134775072</v>
+        <v>134775047</v>
       </c>
       <c r="B146" t="n">
         <v>101403</v>
@@ -17900,10 +17840,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>700154</v>
+        <v>700104</v>
       </c>
       <c r="R146" t="n">
-        <v>6687033</v>
+        <v>6687135</v>
       </c>
       <c r="S146" t="n">
         <v>5</v>
@@ -17935,7 +17875,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -17945,7 +17885,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17971,13 +17911,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775072</t>
+          <t>https://artportalen.se/Sighting/134775047</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134775073</v>
+        <v>134775049</v>
       </c>
       <c r="B147" t="n">
         <v>101403</v>
@@ -18012,10 +17952,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>700175</v>
+        <v>700159</v>
       </c>
       <c r="R147" t="n">
-        <v>6687057</v>
+        <v>6687105</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -18047,7 +17987,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -18057,7 +17997,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -18083,13 +18023,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775073</t>
+          <t>https://artportalen.se/Sighting/134775049</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>134775074</v>
+        <v>134775052</v>
       </c>
       <c r="B148" t="n">
         <v>101403</v>
@@ -18124,10 +18064,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>700201</v>
+        <v>700094</v>
       </c>
       <c r="R148" t="n">
-        <v>6687084</v>
+        <v>6687107</v>
       </c>
       <c r="S148" t="n">
         <v>5</v>
@@ -18159,7 +18099,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -18169,7 +18109,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -18195,13 +18135,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775074</t>
+          <t>https://artportalen.se/Sighting/134775052</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>134775075</v>
+        <v>134775059</v>
       </c>
       <c r="B149" t="n">
         <v>101403</v>
@@ -18236,10 +18176,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>700259</v>
+        <v>700117</v>
       </c>
       <c r="R149" t="n">
-        <v>6687016</v>
+        <v>6687077</v>
       </c>
       <c r="S149" t="n">
         <v>5</v>
@@ -18271,7 +18211,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -18281,7 +18221,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -18307,13 +18247,13 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775075</t>
+          <t>https://artportalen.se/Sighting/134775059</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>134775085</v>
+        <v>134775060</v>
       </c>
       <c r="B150" t="n">
         <v>101403</v>
@@ -18348,10 +18288,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>700182</v>
+        <v>700141</v>
       </c>
       <c r="R150" t="n">
-        <v>6686956</v>
+        <v>6687078</v>
       </c>
       <c r="S150" t="n">
         <v>5</v>
@@ -18383,7 +18323,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -18393,7 +18333,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -18419,13 +18359,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775085</t>
+          <t>https://artportalen.se/Sighting/134775060</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134775088</v>
+        <v>134775068</v>
       </c>
       <c r="B151" t="n">
         <v>101403</v>
@@ -18460,10 +18400,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>700186</v>
+        <v>700149</v>
       </c>
       <c r="R151" t="n">
-        <v>6686937</v>
+        <v>6687048</v>
       </c>
       <c r="S151" t="n">
         <v>5</v>
@@ -18495,7 +18435,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -18505,7 +18445,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -18531,13 +18471,13 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775088</t>
+          <t>https://artportalen.se/Sighting/134775068</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>134775098</v>
+        <v>134775072</v>
       </c>
       <c r="B152" t="n">
         <v>101403</v>
@@ -18572,10 +18512,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>700125</v>
+        <v>700154</v>
       </c>
       <c r="R152" t="n">
-        <v>6686879</v>
+        <v>6687033</v>
       </c>
       <c r="S152" t="n">
         <v>5</v>
@@ -18607,7 +18547,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -18617,7 +18557,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18643,13 +18583,13 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775098</t>
+          <t>https://artportalen.se/Sighting/134775072</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>134775102</v>
+        <v>134775073</v>
       </c>
       <c r="B153" t="n">
         <v>101403</v>
@@ -18684,10 +18624,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>700117</v>
+        <v>700175</v>
       </c>
       <c r="R153" t="n">
-        <v>6686870</v>
+        <v>6687057</v>
       </c>
       <c r="S153" t="n">
         <v>5</v>
@@ -18719,7 +18659,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -18729,7 +18669,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18755,13 +18695,13 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775102</t>
+          <t>https://artportalen.se/Sighting/134775073</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>134775108</v>
+        <v>134775074</v>
       </c>
       <c r="B154" t="n">
         <v>101403</v>
@@ -18796,10 +18736,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>700176</v>
+        <v>700201</v>
       </c>
       <c r="R154" t="n">
-        <v>6686895</v>
+        <v>6687084</v>
       </c>
       <c r="S154" t="n">
         <v>5</v>
@@ -18831,7 +18771,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -18841,7 +18781,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18867,13 +18807,13 @@
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775108</t>
+          <t>https://artportalen.se/Sighting/134775074</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>134775110</v>
+        <v>134775075</v>
       </c>
       <c r="B155" t="n">
         <v>101403</v>
@@ -18908,10 +18848,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>700212</v>
+        <v>700259</v>
       </c>
       <c r="R155" t="n">
-        <v>6686906</v>
+        <v>6687016</v>
       </c>
       <c r="S155" t="n">
         <v>5</v>
@@ -18943,7 +18883,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -18953,7 +18893,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18979,16 +18919,16 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134775110</t>
+          <t>https://artportalen.se/Sighting/134775075</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>134774677</v>
+        <v>134775085</v>
       </c>
       <c r="B156" t="n">
-        <v>99113</v>
+        <v>101403</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18996,21 +18936,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>223591</v>
+        <v>222498</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -19020,10 +18960,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>699623</v>
+        <v>700182</v>
       </c>
       <c r="R156" t="n">
-        <v>6687377</v>
+        <v>6686956</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -19055,7 +18995,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -19065,7 +19005,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -19090,6 +19030,678 @@
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775085</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>134775088</v>
+      </c>
+      <c r="B157" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Sladdarön, Upl</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>700186</v>
+      </c>
+      <c r="R157" t="n">
+        <v>6686937</v>
+      </c>
+      <c r="S157" t="n">
+        <v>5</v>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG157" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="inlineStr"/>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775088</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>134775098</v>
+      </c>
+      <c r="B158" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Sladdarön, Upl</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>700125</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6686879</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775098</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>134775102</v>
+      </c>
+      <c r="B159" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Sladdarön, Upl</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>700117</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6686870</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775102</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>134775108</v>
+      </c>
+      <c r="B160" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Sladdarön, Upl</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>700176</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6686895</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775108</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>134775110</v>
+      </c>
+      <c r="B161" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Sladdarön, Upl</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>700212</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6686906</v>
+      </c>
+      <c r="S161" t="n">
+        <v>5</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134775110</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>134774677</v>
+      </c>
+      <c r="B162" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Sladdarön, Upl</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>699623</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6687377</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Gräsö</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134774677</t>
         </is>
@@ -19252,6 +19864,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92512</v>
+        <v>92513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111635</v>
+        <v>111636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99364</v>
+        <v>99365</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
